--- a/Results_experiment/exp_4/preds_1111114442222222.xlsx
+++ b/Results_experiment/exp_4/preds_1111114442222222.xlsx
@@ -1179,7 +1179,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D2">
-        <v>2.016499757766724</v>
+        <v>1.754421949386597</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D3">
-        <v>3.838138341903687</v>
+        <v>6.705586910247803</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1207,7 +1207,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D4">
-        <v>2.605803489685059</v>
+        <v>2.290393352508545</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>1.550066471099854</v>
+        <v>2.240637063980103</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D6">
-        <v>1.902414083480835</v>
+        <v>4.143164157867432</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1249,7 +1249,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>4.167122840881348</v>
+        <v>7.868288516998291</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1263,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>2.615133285522461</v>
+        <v>2.418490409851074</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D9">
-        <v>8.562854766845703</v>
+        <v>11.31188297271729</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D10">
-        <v>6.913505077362061</v>
+        <v>9.862591743469238</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1305,7 +1305,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D11">
-        <v>2.379026889801025</v>
+        <v>1.859039545059204</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D12">
-        <v>1.935624957084656</v>
+        <v>1.694620132446289</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D13">
-        <v>9.554520606994629</v>
+        <v>11.25514030456543</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1347,7 +1347,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D14">
-        <v>2.514616012573242</v>
+        <v>2.550931215286255</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1361,7 +1361,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D15">
-        <v>2.236482381820679</v>
+        <v>2.045137882232666</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1375,7 +1375,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D16">
-        <v>2.107134342193604</v>
+        <v>2.466873168945312</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D17">
-        <v>1.526715874671936</v>
+        <v>1.855415344238281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1403,7 +1403,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D18">
-        <v>9.855439186096191</v>
+        <v>10.55300807952881</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1417,7 +1417,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D19">
-        <v>1.846810698509216</v>
+        <v>2.65094256401062</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1431,7 +1431,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D20">
-        <v>8.033041954040527</v>
+        <v>9.290413856506348</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1445,7 +1445,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D21">
-        <v>2.39398193359375</v>
+        <v>2.139311075210571</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1459,7 +1459,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D22">
-        <v>2.675442934036255</v>
+        <v>2.027486085891724</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1473,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>2.33251953125</v>
+        <v>1.989522933959961</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1487,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="D24">
-        <v>3.464447498321533</v>
+        <v>2.581527471542358</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1501,7 +1501,7 @@
         <v>14.5</v>
       </c>
       <c r="D25">
-        <v>6.382387161254883</v>
+        <v>5.003795623779297</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>2.042404651641846</v>
+        <v>2.574989557266235</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1529,7 +1529,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D27">
-        <v>2.388162136077881</v>
+        <v>2.108748435974121</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1543,7 +1543,7 @@
         <v>26.89999961853027</v>
       </c>
       <c r="D28">
-        <v>16.09504127502441</v>
+        <v>11.50098514556885</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1557,7 +1557,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D29">
-        <v>3.731092929840088</v>
+        <v>4.626804351806641</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1571,7 +1571,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D30">
-        <v>2.380177736282349</v>
+        <v>2.198765277862549</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1585,7 +1585,7 @@
         <v>10.5</v>
       </c>
       <c r="D31">
-        <v>1.926178216934204</v>
+        <v>5.896294116973877</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1599,7 +1599,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D32">
-        <v>1.886895179748535</v>
+        <v>8.951249122619629</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1613,7 +1613,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D33">
-        <v>6.383359909057617</v>
+        <v>6.892148494720459</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1627,7 +1627,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D34">
-        <v>2.015224933624268</v>
+        <v>2.452250242233276</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1641,7 +1641,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D35">
-        <v>3.047832250595093</v>
+        <v>3.266985893249512</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1655,7 +1655,7 @@
         <v>6.5</v>
       </c>
       <c r="D36">
-        <v>4.800457954406738</v>
+        <v>5.842226505279541</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1669,7 +1669,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D37">
-        <v>2.209708213806152</v>
+        <v>2.438926935195923</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1683,7 +1683,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D38">
-        <v>5.665561676025391</v>
+        <v>8.207314491271973</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1697,7 +1697,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D39">
-        <v>7.286679267883301</v>
+        <v>10.40278053283691</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1711,7 +1711,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D40">
-        <v>4.219361782073975</v>
+        <v>3.227314233779907</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1725,7 +1725,7 @@
         <v>1.5</v>
       </c>
       <c r="D41">
-        <v>3.132120132446289</v>
+        <v>3.617141008377075</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1739,7 +1739,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D42">
-        <v>2.141222476959229</v>
+        <v>1.706233620643616</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1753,7 +1753,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D43">
-        <v>2.176477670669556</v>
+        <v>1.972804307937622</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1767,7 +1767,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D44">
-        <v>1.938201427459717</v>
+        <v>1.670764803886414</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1781,7 +1781,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>4.799093723297119</v>
+        <v>6.71139669418335</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1795,7 +1795,7 @@
         <v>3.5</v>
       </c>
       <c r="D46">
-        <v>2.171226024627686</v>
+        <v>1.687069177627563</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1809,7 +1809,7 @@
         <v>0.5</v>
       </c>
       <c r="D47">
-        <v>2.509490966796875</v>
+        <v>1.870633840560913</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1823,7 +1823,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D48">
-        <v>2.337927341461182</v>
+        <v>1.833725690841675</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1837,7 +1837,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D49">
-        <v>2.640066146850586</v>
+        <v>2.308489799499512</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1851,7 +1851,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="D50">
-        <v>6.01464319229126</v>
+        <v>4.90036153793335</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1865,7 +1865,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>3.625443935394287</v>
+        <v>2.132954835891724</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1879,7 +1879,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D52">
-        <v>2.699993133544922</v>
+        <v>3.518229484558105</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1893,7 +1893,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D53">
-        <v>3.893129825592041</v>
+        <v>5.102676868438721</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>5.61843729019165</v>
+        <v>6.711335182189941</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D55">
-        <v>2.167716979980469</v>
+        <v>2.24880838394165</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D56">
-        <v>2.631773710250854</v>
+        <v>4.469803333282471</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D57">
-        <v>2.119584321975708</v>
+        <v>2.553139925003052</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D58">
-        <v>1.804054260253906</v>
+        <v>2.516790151596069</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.285145282745361</v>
+        <v>2.158671617507935</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D60">
-        <v>2.256666421890259</v>
+        <v>2.253416061401367</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="D61">
-        <v>2.020370006561279</v>
+        <v>1.670238494873047</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D62">
-        <v>6.966643333435059</v>
+        <v>7.015148162841797</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D63">
-        <v>2.159976482391357</v>
+        <v>2.49805760383606</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D64">
-        <v>2.273444652557373</v>
+        <v>1.734323263168335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2061,7 +2061,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D65">
-        <v>3.050704956054688</v>
+        <v>2.93964409828186</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2075,7 +2075,7 @@
         <v>3.5</v>
       </c>
       <c r="D66">
-        <v>2.692747116088867</v>
+        <v>1.966833114624023</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2089,7 +2089,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D67">
-        <v>2.256409406661987</v>
+        <v>2.761546611785889</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2103,7 +2103,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D68">
-        <v>2.52591609954834</v>
+        <v>2.03390645980835</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2117,7 +2117,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>2.145636320114136</v>
+        <v>1.891029119491577</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D70">
-        <v>1.895411133766174</v>
+        <v>3.246723175048828</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="D71">
-        <v>1.626638412475586</v>
+        <v>3.458940744400024</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D72">
-        <v>3.9701087474823</v>
+        <v>4.120341300964355</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2173,7 +2173,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D73">
-        <v>4.451905250549316</v>
+        <v>6.650221347808838</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>4.269970893859863</v>
+        <v>4.278810024261475</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2201,7 +2201,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D75">
-        <v>2.024322271347046</v>
+        <v>2.44451642036438</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2215,7 +2215,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D76">
-        <v>6.433969020843506</v>
+        <v>7.851871967315674</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2229,7 +2229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D77">
-        <v>4.863909244537354</v>
+        <v>4.535707950592041</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2243,7 +2243,7 @@
         <v>3.5</v>
       </c>
       <c r="D78">
-        <v>1.94653058052063</v>
+        <v>2.692750215530396</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2257,7 +2257,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.761319398880005</v>
+        <v>2.18230128288269</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2271,7 +2271,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D80">
-        <v>3.116065979003906</v>
+        <v>3.348028421401978</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2285,7 +2285,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D81">
-        <v>4.546914577484131</v>
+        <v>6.670514583587646</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D82">
-        <v>5.109126091003418</v>
+        <v>5.32550573348999</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2313,7 +2313,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D83">
-        <v>2.257291555404663</v>
+        <v>2.591968059539795</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2327,7 +2327,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D84">
-        <v>3.263062000274658</v>
+        <v>3.526999235153198</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2341,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>2.541164875030518</v>
+        <v>2.702174186706543</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2355,7 +2355,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D86">
-        <v>2.34284782409668</v>
+        <v>3.344633340835571</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2369,7 +2369,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D87">
-        <v>1.693159580230713</v>
+        <v>1.812361240386963</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2383,7 +2383,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D88">
-        <v>4.422451496124268</v>
+        <v>5.296779155731201</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2397,7 +2397,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D89">
-        <v>2.129692077636719</v>
+        <v>1.966606140136719</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2411,7 +2411,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D90">
-        <v>2.076539039611816</v>
+        <v>1.852952480316162</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2425,7 +2425,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>9.10755443572998</v>
+        <v>13.46964740753174</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2439,7 +2439,7 @@
         <v>0.5</v>
       </c>
       <c r="D92">
-        <v>4.087002277374268</v>
+        <v>5.283302783966064</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
       <c r="D93">
-        <v>5.449838161468506</v>
+        <v>8.440649032592773</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>2.25798225402832</v>
+        <v>3.259854078292847</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2481,7 +2481,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D95">
-        <v>1.8965083360672</v>
+        <v>1.760280132293701</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2495,7 +2495,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D96">
-        <v>2.726754903793335</v>
+        <v>2.965749263763428</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2509,7 +2509,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D97">
-        <v>5.8636794090271</v>
+        <v>5.303451061248779</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2523,7 +2523,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D98">
-        <v>6.078185558319092</v>
+        <v>8.898510932922363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2537,7 +2537,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D99">
-        <v>2.28187894821167</v>
+        <v>1.900434017181396</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2551,7 +2551,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D100">
-        <v>2.070992708206177</v>
+        <v>3.376036405563354</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2565,7 +2565,7 @@
         <v>4.5</v>
       </c>
       <c r="D101">
-        <v>2.703269481658936</v>
+        <v>3.668665885925293</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D102">
-        <v>1.935349702835083</v>
+        <v>3.409087419509888</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D103">
-        <v>2.394636631011963</v>
+        <v>1.778595209121704</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2607,7 +2607,7 @@
         <v>10.5</v>
       </c>
       <c r="D104">
-        <v>4.12590503692627</v>
+        <v>6.967384338378906</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D105">
-        <v>1.639139890670776</v>
+        <v>2.749932765960693</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2635,7 +2635,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D106">
-        <v>2.498188257217407</v>
+        <v>1.669528245925903</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2649,7 +2649,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D107">
-        <v>8.987305641174316</v>
+        <v>9.281183242797852</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2663,7 +2663,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D108">
-        <v>5.974899291992188</v>
+        <v>9.048186302185059</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2677,7 +2677,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D109">
-        <v>7.691397666931152</v>
+        <v>8.051847457885742</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2691,7 +2691,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D110">
-        <v>4.913483142852783</v>
+        <v>6.303075313568115</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D111">
-        <v>6.427300453186035</v>
+        <v>8.408906936645508</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2719,7 +2719,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D112">
-        <v>2.766438245773315</v>
+        <v>2.939903259277344</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D113">
-        <v>2.19096851348877</v>
+        <v>2.736237764358521</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="D114">
-        <v>2.831591129302979</v>
+        <v>2.354778051376343</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2761,7 +2761,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D115">
-        <v>2.267452716827393</v>
+        <v>2.069036245346069</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="D116">
-        <v>15.28402328491211</v>
+        <v>14.5292272567749</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D117">
-        <v>1.683140397071838</v>
+        <v>2.290799379348755</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2803,7 +2803,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D118">
-        <v>3.203656673431396</v>
+        <v>3.813308954238892</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2817,7 +2817,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D119">
-        <v>3.28569507598877</v>
+        <v>3.931093692779541</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2831,7 +2831,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D120">
-        <v>4.116019248962402</v>
+        <v>10.44111728668213</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2845,7 +2845,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D121">
-        <v>2.035618543624878</v>
+        <v>2.583911418914795</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>20.10000038146973</v>
       </c>
       <c r="D122">
-        <v>3.176845550537109</v>
+        <v>5.959019184112549</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>6.5</v>
       </c>
       <c r="D123">
-        <v>6.428030490875244</v>
+        <v>5.749521255493164</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2887,7 +2887,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D124">
-        <v>2.125961303710938</v>
+        <v>1.835801362991333</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2901,7 +2901,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D125">
-        <v>1.764265060424805</v>
+        <v>1.70695972442627</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D126">
-        <v>2.094476222991943</v>
+        <v>1.82861602306366</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D127">
-        <v>3.819683074951172</v>
+        <v>4.3946852684021</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2943,7 +2943,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D128">
-        <v>2.807319641113281</v>
+        <v>3.703371286392212</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2957,7 +2957,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D129">
-        <v>3.809627532958984</v>
+        <v>2.191972017288208</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2971,7 +2971,7 @@
         <v>0.5</v>
       </c>
       <c r="D130">
-        <v>3.548134326934814</v>
+        <v>3.048620462417603</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D131">
-        <v>2.387013912200928</v>
+        <v>2.011987209320068</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>2.5</v>
       </c>
       <c r="D132">
-        <v>2.129411220550537</v>
+        <v>2.149350166320801</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="D133">
-        <v>18.18564605712891</v>
+        <v>19.02305030822754</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3027,7 +3027,7 @@
         <v>0.5</v>
       </c>
       <c r="D134">
-        <v>1.934517383575439</v>
+        <v>2.681767463684082</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D135">
-        <v>5.908571243286133</v>
+        <v>7.413907051086426</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>18.70000076293945</v>
       </c>
       <c r="D136">
-        <v>10.01903057098389</v>
+        <v>11.025634765625</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D137">
-        <v>2.461441516876221</v>
+        <v>2.757214069366455</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D138">
-        <v>4.319625854492188</v>
+        <v>7.953114986419678</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3097,7 +3097,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D139">
-        <v>3.806982278823853</v>
+        <v>6.417337894439697</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D140">
-        <v>2.09337854385376</v>
+        <v>2.707192659378052</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D141">
-        <v>7.354015827178955</v>
+        <v>6.995990753173828</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D142">
-        <v>1.683125972747803</v>
+        <v>2.075223445892334</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D143">
-        <v>5.636022090911865</v>
+        <v>7.771111011505127</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D144">
-        <v>2.140604496002197</v>
+        <v>3.029287099838257</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>2.5</v>
       </c>
       <c r="D145">
-        <v>2.078012228012085</v>
+        <v>1.895630836486816</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D146">
-        <v>6.439308643341064</v>
+        <v>8.122031211853027</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>13.5</v>
       </c>
       <c r="D147">
-        <v>8.521274566650391</v>
+        <v>11.00358772277832</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D148">
-        <v>2.301535367965698</v>
+        <v>6.875441074371338</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D149">
-        <v>2.376941204071045</v>
+        <v>1.92539119720459</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D150">
-        <v>7.603316307067871</v>
+        <v>8.775750160217285</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D151">
-        <v>4.476838111877441</v>
+        <v>6.273724555969238</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D152">
-        <v>2.123135089874268</v>
+        <v>2.565274715423584</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D153">
-        <v>6.022798538208008</v>
+        <v>5.286475658416748</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D154">
-        <v>1.953290224075317</v>
+        <v>1.667157411575317</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>1.5</v>
       </c>
       <c r="D155">
-        <v>2.017295360565186</v>
+        <v>2.201808929443359</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D156">
-        <v>3.461804628372192</v>
+        <v>2.73784351348877</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D157">
-        <v>1.925181150436401</v>
+        <v>1.786994338035583</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="D158">
-        <v>4.089405536651611</v>
+        <v>6.143851280212402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D159">
-        <v>1.744783043861389</v>
+        <v>2.367164850234985</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>2.978259563446045</v>
+        <v>2.240447521209717</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="D161">
-        <v>8.287251472473145</v>
+        <v>6.641809940338135</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D162">
-        <v>2.001052856445312</v>
+        <v>6.31926965713501</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D163">
-        <v>3.209139347076416</v>
+        <v>3.038618326187134</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>1.832329273223877</v>
+        <v>2.097869873046875</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D165">
-        <v>1.825951218605042</v>
+        <v>6.192345142364502</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>4.5</v>
       </c>
       <c r="D166">
-        <v>2.331051349639893</v>
+        <v>2.582032203674316</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3489,7 +3489,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D167">
-        <v>2.652821779251099</v>
+        <v>2.992995262145996</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3503,7 +3503,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D168">
-        <v>6.023185729980469</v>
+        <v>6.705518245697021</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="D169">
-        <v>2.451356410980225</v>
+        <v>2.077458381652832</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>1.5</v>
       </c>
       <c r="D170">
-        <v>3.002310752868652</v>
+        <v>3.552391767501831</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D171">
-        <v>3.775089979171753</v>
+        <v>6.648178100585938</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D172">
-        <v>2.352507829666138</v>
+        <v>2.326502561569214</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>10.5</v>
       </c>
       <c r="D173">
-        <v>8.744709014892578</v>
+        <v>9.643725395202637</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D174">
-        <v>2.900604724884033</v>
+        <v>3.338401556015015</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D175">
-        <v>4.324275970458984</v>
+        <v>5.820542335510254</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D176">
-        <v>2.534178733825684</v>
+        <v>3.554084777832031</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D177">
-        <v>2.32110071182251</v>
+        <v>1.868074893951416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D178">
-        <v>2.172836303710938</v>
+        <v>3.758078336715698</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D179">
-        <v>2.222322940826416</v>
+        <v>2.306344509124756</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>2.428800106048584</v>
+        <v>3.005768060684204</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D181">
-        <v>2.113159656524658</v>
+        <v>7.224387645721436</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="D182">
-        <v>2.185609102249146</v>
+        <v>1.907939195632935</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D183">
-        <v>2.079555511474609</v>
+        <v>3.615119695663452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D184">
-        <v>5.060493946075439</v>
+        <v>6.636809825897217</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>2.769226789474487</v>
+        <v>3.172266244888306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D186">
-        <v>1.899372816085815</v>
+        <v>3.277686834335327</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D187">
-        <v>6.539921283721924</v>
+        <v>6.786863327026367</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D188">
-        <v>2.261296987533569</v>
+        <v>2.137710094451904</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3797,7 +3797,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D189">
-        <v>1.684567451477051</v>
+        <v>4.172820091247559</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D190">
-        <v>2.064057111740112</v>
+        <v>3.200457811355591</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>1.5</v>
       </c>
       <c r="D191">
-        <v>2.135499954223633</v>
+        <v>2.064173936843872</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>2.323779106140137</v>
+        <v>2.121984481811523</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D193">
-        <v>2.458909511566162</v>
+        <v>3.162476778030396</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3867,7 +3867,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D194">
-        <v>9.172513961791992</v>
+        <v>10.05777072906494</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3881,7 +3881,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D195">
-        <v>7.073043823242188</v>
+        <v>5.786782741546631</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="D196">
-        <v>2.481034278869629</v>
+        <v>3.201024770736694</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D197">
-        <v>5.333742141723633</v>
+        <v>6.46263599395752</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>2.5</v>
       </c>
       <c r="D198">
-        <v>2.251702070236206</v>
+        <v>1.826038956642151</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D199">
-        <v>4.496665000915527</v>
+        <v>6.178480625152588</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D200">
-        <v>2.131170272827148</v>
+        <v>3.269545793533325</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>8.5</v>
       </c>
       <c r="D201">
-        <v>1.785216808319092</v>
+        <v>3.5417799949646</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D202">
-        <v>5.261452674865723</v>
+        <v>6.661966800689697</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3993,7 +3993,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D203">
-        <v>3.815153121948242</v>
+        <v>4.784308910369873</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>1.84127950668335</v>
+        <v>3.422891616821289</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4021,7 +4021,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D205">
-        <v>10.03760623931885</v>
+        <v>14.23848724365234</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D206">
-        <v>1.883239269256592</v>
+        <v>2.506092548370361</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D207">
-        <v>2.854133129119873</v>
+        <v>6.585990428924561</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D208">
-        <v>4.661656856536865</v>
+        <v>5.334853649139404</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D209">
-        <v>2.063992261886597</v>
+        <v>2.462865114212036</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D210">
-        <v>2.208450794219971</v>
+        <v>1.713995814323425</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D211">
-        <v>4.972421169281006</v>
+        <v>6.66523551940918</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D212">
-        <v>4.106051921844482</v>
+        <v>5.243154048919678</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4133,7 +4133,7 @@
         <v>1.5</v>
       </c>
       <c r="D213">
-        <v>2.681245565414429</v>
+        <v>1.898839950561523</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D214">
-        <v>8.096479415893555</v>
+        <v>10.48622226715088</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D215">
-        <v>3.602830410003662</v>
+        <v>5.794009685516357</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D216">
-        <v>3.726387977600098</v>
+        <v>2.593365430831909</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D217">
-        <v>2.059586048126221</v>
+        <v>2.729557037353516</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D218">
-        <v>6.845173835754395</v>
+        <v>7.06816577911377</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>4.5</v>
       </c>
       <c r="D219">
-        <v>2.380188703536987</v>
+        <v>2.342409372329712</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D220">
-        <v>1.583181858062744</v>
+        <v>2.19213080406189</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D221">
-        <v>5.771624088287354</v>
+        <v>7.011169910430908</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D222">
-        <v>5.959324836730957</v>
+        <v>9.718653678894043</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D223">
-        <v>2.377615451812744</v>
+        <v>2.121346473693848</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D224">
-        <v>3.135370969772339</v>
+        <v>7.057161331176758</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D225">
-        <v>2.248933792114258</v>
+        <v>2.168211936950684</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>2.036090850830078</v>
+        <v>1.833927154541016</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="D227">
-        <v>2.332661151885986</v>
+        <v>1.968876600265503</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D228">
-        <v>2.131753921508789</v>
+        <v>1.876050472259521</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D229">
-        <v>5.964939117431641</v>
+        <v>6.409802913665771</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D230">
-        <v>2.549701929092407</v>
+        <v>2.590891122817993</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>2.904784202575684</v>
+        <v>2.006541728973389</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D232">
-        <v>7.177838325500488</v>
+        <v>11.42948532104492</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D233">
-        <v>2.295830011367798</v>
+        <v>2.310514211654663</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D234">
-        <v>2.32234525680542</v>
+        <v>2.504104852676392</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D235">
-        <v>3.68708610534668</v>
+        <v>6.647957324981689</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>4.201361179351807</v>
+        <v>6.141348838806152</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D237">
-        <v>1.855253934860229</v>
+        <v>2.470296859741211</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D238">
-        <v>2.144750833511353</v>
+        <v>2.880750894546509</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>3.5</v>
       </c>
       <c r="D239">
-        <v>4.670069217681885</v>
+        <v>5.811801433563232</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D240">
-        <v>2.303592681884766</v>
+        <v>2.466851472854614</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D241">
-        <v>2.14177942276001</v>
+        <v>2.47104024887085</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D242">
-        <v>2.14340353012085</v>
+        <v>2.086087465286255</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D243">
-        <v>2.123175621032715</v>
+        <v>3.180116415023804</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>5</v>
       </c>
       <c r="D244">
-        <v>3.738801956176758</v>
+        <v>6.147995471954346</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D245">
-        <v>9.128060340881348</v>
+        <v>13.30263233184814</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4595,7 +4595,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D246">
-        <v>5.53632116317749</v>
+        <v>6.102116107940674</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D247">
-        <v>1.918996810913086</v>
+        <v>1.688069343566895</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D248">
-        <v>4.578496932983398</v>
+        <v>6.454532623291016</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4637,7 +4637,7 @@
         <v>6.5</v>
       </c>
       <c r="D249">
-        <v>1.984307408332825</v>
+        <v>1.861583471298218</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D250">
-        <v>2.390447854995728</v>
+        <v>2.097937822341919</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>2.5</v>
       </c>
       <c r="D251">
-        <v>2.151172876358032</v>
+        <v>1.630902051925659</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>3.913013935089111</v>
+        <v>3.62157940864563</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D253">
-        <v>4.365362644195557</v>
+        <v>5.989808559417725</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>4.74519681930542</v>
+        <v>6.716855525970459</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D255">
-        <v>5.371137142181396</v>
+        <v>6.247529983520508</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D256">
-        <v>2.526207208633423</v>
+        <v>1.794757604598999</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D257">
-        <v>2.510003805160522</v>
+        <v>2.07885479927063</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4763,7 +4763,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>2.243356466293335</v>
+        <v>1.69850742816925</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D259">
-        <v>2.333098411560059</v>
+        <v>1.977629661560059</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D260">
-        <v>2.478438377380371</v>
+        <v>1.964894533157349</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>9.5</v>
       </c>
       <c r="D261">
-        <v>4.625581741333008</v>
+        <v>5.85529088973999</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D262">
-        <v>2.636562347412109</v>
+        <v>2.418948650360107</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4833,7 +4833,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D263">
-        <v>2.467829465866089</v>
+        <v>2.098695039749146</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D264">
-        <v>4.96184253692627</v>
+        <v>6.050965309143066</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D265">
-        <v>2.240161418914795</v>
+        <v>2.904863119125366</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D266">
-        <v>5.289138793945312</v>
+        <v>6.650884628295898</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D267">
-        <v>2.044838428497314</v>
+        <v>4.223024845123291</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D268">
-        <v>2.926655769348145</v>
+        <v>3.577187299728394</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D269">
-        <v>7.355059146881104</v>
+        <v>5.199167728424072</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D270">
-        <v>2.197229623794556</v>
+        <v>2.005303621292114</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D271">
-        <v>3.100252151489258</v>
+        <v>2.575060129165649</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D272">
-        <v>2.262976884841919</v>
+        <v>2.796776533126831</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4973,7 +4973,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D273">
-        <v>3.964197635650635</v>
+        <v>6.608939170837402</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D274">
-        <v>5.394834518432617</v>
+        <v>7.074309349060059</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>2.067564964294434</v>
+        <v>1.814367771148682</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D276">
-        <v>3.982359409332275</v>
+        <v>3.227200746536255</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>8.5</v>
       </c>
       <c r="D277">
-        <v>7.394237518310547</v>
+        <v>6.622148036956787</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>0.5</v>
       </c>
       <c r="D278">
-        <v>2.305848598480225</v>
+        <v>9.390631675720215</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D279">
-        <v>5.39501953125</v>
+        <v>6.680755138397217</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D280">
-        <v>1.782788991928101</v>
+        <v>3.282052040100098</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D281">
-        <v>2.349153518676758</v>
+        <v>2.103998422622681</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D282">
-        <v>1.864859104156494</v>
+        <v>1.802569389343262</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D283">
-        <v>2.84750771522522</v>
+        <v>2.557746887207031</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>35.70000076293945</v>
       </c>
       <c r="D284">
-        <v>24.01778030395508</v>
+        <v>26.92885398864746</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D285">
-        <v>3.02918553352356</v>
+        <v>4.612597942352295</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D286">
-        <v>9.20072078704834</v>
+        <v>10.91714286804199</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D287">
-        <v>2.248944759368896</v>
+        <v>1.838890075683594</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>4.317197799682617</v>
+        <v>5.356495380401611</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>0.5</v>
       </c>
       <c r="D289">
-        <v>2.190140247344971</v>
+        <v>1.780425786972046</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D290">
-        <v>2.475458145141602</v>
+        <v>4.429090023040771</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>1.5</v>
       </c>
       <c r="D291">
-        <v>2.182604789733887</v>
+        <v>1.75868809223175</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>2.546261310577393</v>
+        <v>1.854719161987305</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D293">
-        <v>2.154386043548584</v>
+        <v>2.076079607009888</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D294">
-        <v>2.042596817016602</v>
+        <v>2.693302631378174</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5281,7 +5281,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D295">
-        <v>3.814020156860352</v>
+        <v>2.62748122215271</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D296">
-        <v>2.062276363372803</v>
+        <v>2.079745531082153</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5309,7 +5309,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D297">
-        <v>8.139235496520996</v>
+        <v>8.789392471313477</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5323,7 +5323,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D298">
-        <v>2.44240140914917</v>
+        <v>6.179206371307373</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5337,7 +5337,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D299">
-        <v>8.992605209350586</v>
+        <v>9.85921573638916</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="D300">
-        <v>2.552031278610229</v>
+        <v>3.212427854537964</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5365,7 +5365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D301">
-        <v>7.863049507141113</v>
+        <v>12.83305644989014</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5379,7 +5379,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D302">
-        <v>2.249058723449707</v>
+        <v>2.175055503845215</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="D303">
-        <v>5.629398822784424</v>
+        <v>8.765666961669922</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5407,7 +5407,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D304">
-        <v>3.536826133728027</v>
+        <v>4.615624904632568</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D305">
-        <v>2.353592872619629</v>
+        <v>2.176249980926514</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D306">
-        <v>3.343853235244751</v>
+        <v>5.608878612518311</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5449,7 +5449,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D307">
-        <v>2.182577133178711</v>
+        <v>1.729503631591797</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5463,7 +5463,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D308">
-        <v>2.151579618453979</v>
+        <v>1.798361301422119</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5477,7 +5477,7 @@
         <v>1.5</v>
       </c>
       <c r="D309">
-        <v>2.041138410568237</v>
+        <v>1.831848502159119</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5491,7 +5491,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D310">
-        <v>3.0534508228302</v>
+        <v>6.190114974975586</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5505,7 +5505,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D311">
-        <v>2.098546981811523</v>
+        <v>1.888402700424194</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5519,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="D312">
-        <v>1.835883975028992</v>
+        <v>1.868762493133545</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="D313">
-        <v>4.394679546356201</v>
+        <v>5.797852039337158</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5547,7 +5547,7 @@
         <v>2.5</v>
       </c>
       <c r="D314">
-        <v>3.322125673294067</v>
+        <v>3.408118963241577</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5561,7 +5561,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D315">
-        <v>2.071077823638916</v>
+        <v>8.180710792541504</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5575,7 +5575,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D316">
-        <v>1.889169931411743</v>
+        <v>2.4788978099823</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5589,7 +5589,7 @@
         <v>7.5</v>
       </c>
       <c r="D317">
-        <v>2.279249906539917</v>
+        <v>6.206790924072266</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5603,7 +5603,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D318">
-        <v>2.163027286529541</v>
+        <v>2.07156777381897</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5617,7 +5617,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D319">
-        <v>1.960138559341431</v>
+        <v>2.264050722122192</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5631,7 +5631,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D320">
-        <v>7.097057342529297</v>
+        <v>5.670349597930908</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5645,7 +5645,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D321">
-        <v>4.93313455581665</v>
+        <v>3.387959957122803</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5659,7 +5659,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D322">
-        <v>2.470415830612183</v>
+        <v>1.709810972213745</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5673,7 +5673,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D323">
-        <v>2.602583169937134</v>
+        <v>2.514927387237549</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5687,7 +5687,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D324">
-        <v>4.458030700683594</v>
+        <v>4.551519393920898</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5701,7 +5701,7 @@
         <v>7.5</v>
       </c>
       <c r="D325">
-        <v>5.636912822723389</v>
+        <v>3.929215431213379</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5715,7 +5715,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D326">
-        <v>2.085319042205811</v>
+        <v>1.856038093566895</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5729,7 +5729,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D327">
-        <v>2.874428272247314</v>
+        <v>6.357851505279541</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5743,7 +5743,7 @@
         <v>1</v>
       </c>
       <c r="D328">
-        <v>1.820920467376709</v>
+        <v>1.761368751525879</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5757,7 +5757,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D329">
-        <v>2.591285467147827</v>
+        <v>2.680860042572021</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5771,7 +5771,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D330">
-        <v>4.003312110900879</v>
+        <v>6.682848453521729</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5785,7 +5785,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D331">
-        <v>2.277864456176758</v>
+        <v>2.153013467788696</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5799,7 +5799,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>1.902950882911682</v>
+        <v>4.45975399017334</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5813,7 +5813,7 @@
         <v>11</v>
       </c>
       <c r="D333">
-        <v>4.048018455505371</v>
+        <v>5.719671249389648</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5827,7 +5827,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D334">
-        <v>11.23251533508301</v>
+        <v>4.066928863525391</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5841,7 +5841,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D335">
-        <v>4.57848072052002</v>
+        <v>6.218145847320557</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5855,7 +5855,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D336">
-        <v>2.418473720550537</v>
+        <v>2.323314905166626</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5869,7 +5869,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D337">
-        <v>2.04008412361145</v>
+        <v>3.807375192642212</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5883,7 +5883,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D338">
-        <v>4.645540237426758</v>
+        <v>5.940294742584229</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5897,7 +5897,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D339">
-        <v>9.689687728881836</v>
+        <v>13.12680435180664</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5911,7 +5911,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D340">
-        <v>2.426352024078369</v>
+        <v>1.778398513793945</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5925,7 +5925,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D341">
-        <v>3.440554618835449</v>
+        <v>4.485132694244385</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5939,7 +5939,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D342">
-        <v>3.599973917007446</v>
+        <v>4.966112613677979</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5953,7 +5953,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D343">
-        <v>2.261066913604736</v>
+        <v>3.166917085647583</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5967,7 +5967,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D344">
-        <v>2.459203720092773</v>
+        <v>1.694801568984985</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5981,7 +5981,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D345">
-        <v>6.501459121704102</v>
+        <v>6.92470121383667</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5995,7 +5995,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D346">
-        <v>5.03025484085083</v>
+        <v>7.182887077331543</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6009,7 +6009,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D347">
-        <v>2.520214080810547</v>
+        <v>2.083879947662354</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6023,7 +6023,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D348">
-        <v>5.664456367492676</v>
+        <v>7.703882694244385</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6037,7 +6037,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>2.383249759674072</v>
+        <v>2.499562978744507</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6051,7 +6051,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D350">
-        <v>5.565051078796387</v>
+        <v>6.583962917327881</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6065,7 +6065,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D351">
-        <v>2.437631130218506</v>
+        <v>2.115080595016479</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6079,7 +6079,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D352">
-        <v>3.058244943618774</v>
+        <v>3.492136716842651</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6093,7 +6093,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>12.31009006500244</v>
+        <v>14.01915168762207</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6107,7 +6107,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D354">
-        <v>2.329105854034424</v>
+        <v>1.984416484832764</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6121,7 +6121,7 @@
         <v>15.5</v>
       </c>
       <c r="D355">
-        <v>6.881112098693848</v>
+        <v>7.296337604522705</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6135,7 +6135,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D356">
-        <v>2.394461631774902</v>
+        <v>1.836769342422485</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6149,7 +6149,7 @@
         <v>1.5</v>
       </c>
       <c r="D357">
-        <v>3.950701236724854</v>
+        <v>3.790964365005493</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6163,7 +6163,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D358">
-        <v>2.264002799987793</v>
+        <v>7.864734649658203</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6177,7 +6177,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D359">
-        <v>5.468005657196045</v>
+        <v>5.27679967880249</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6191,7 +6191,7 @@
         <v>5.5</v>
       </c>
       <c r="D360">
-        <v>2.578977584838867</v>
+        <v>2.761920690536499</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>2.31148624420166</v>
+        <v>2.462693214416504</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6219,7 +6219,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D362">
-        <v>7.430434226989746</v>
+        <v>7.261520385742188</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6233,7 +6233,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D363">
-        <v>10.46289348602295</v>
+        <v>11.97360324859619</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6247,7 +6247,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D364">
-        <v>2.388318061828613</v>
+        <v>2.933305501937866</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6261,7 +6261,7 @@
         <v>1.5</v>
       </c>
       <c r="D365">
-        <v>1.645478963851929</v>
+        <v>1.917894840240479</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6275,7 +6275,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D366">
-        <v>2.106274843215942</v>
+        <v>1.823400497436523</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6289,7 +6289,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D367">
-        <v>3.738610506057739</v>
+        <v>5.07521915435791</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6303,7 +6303,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D368">
-        <v>8.199522018432617</v>
+        <v>12.64051342010498</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6317,7 +6317,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D369">
-        <v>2.420480728149414</v>
+        <v>1.853689670562744</v>
       </c>
     </row>
   </sheetData>
